--- a/SHET/ZPO001/zpovn1.xlsx
+++ b/SHET/ZPO001/zpovn1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30F8D506-9372-45E3-9FC7-FFB1A3C1761A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5189536-D3A8-411D-AA69-63482A7E9046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,10 +132,10 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -480,10 +480,12 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="13.7109375" customWidth="1"/>
-    <col min="3" max="4" width="26.140625" customWidth="1"/>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" customWidth="1"/>
     <col min="5" max="5" width="21.42578125" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" customWidth="1"/>
+    <col min="6" max="6" width="39.7109375" customWidth="1"/>
     <col min="7" max="7" width="16.42578125" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
     <col min="9" max="9" width="13.7109375" customWidth="1"/>
@@ -492,50 +494,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2" t="s">
+      <c r="F1" s="3"/>
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="2"/>
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="3"/>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -544,7 +546,7 @@
       <c r="B3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
@@ -555,7 +557,7 @@
       <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="3"/>
+      <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -564,7 +566,7 @@
       <c r="B5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C5" s="3"/>
+      <c r="C5" s="2"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
@@ -573,7 +575,7 @@
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>20</v>
       </c>
     </row>
@@ -584,7 +586,7 @@
       <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3"/>
+      <c r="C7" s="2"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
@@ -593,10 +595,14 @@
       <c r="B8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="3"/>
+      <c r="C8" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
     <mergeCell ref="C6:C8"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="H1:H2"/>
@@ -604,10 +610,6 @@
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="C3:C5"/>
     <mergeCell ref="E1:F1"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/SHET/ZPO001/zpovn1.xlsx
+++ b/SHET/ZPO001/zpovn1.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5189536-D3A8-411D-AA69-63482A7E9046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1373AF5E-78C8-4EEB-AA1A-4EA1EBEB0157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,16 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
-  <si>
-    <t>Ток</t>
-  </si>
-  <si>
-    <t>Воздействие</t>
-  </si>
-  <si>
-    <t>Контр. сигнал</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="25">
   <si>
     <t>Уставка I&gt;, А</t>
   </si>
@@ -90,6 +81,21 @@
   </si>
   <si>
     <t>Проверка тока срабатывания и коэффициента возврата ИО стороны ВН</t>
+  </si>
+  <si>
+    <t>Вход для проверки</t>
+  </si>
+  <si>
+    <t>Сигнал</t>
+  </si>
+  <si>
+    <t>Выход для контроля</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>ТС</t>
   </si>
 </sst>
 </file>
@@ -132,10 +138,10 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -477,7 +483,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
@@ -485,7 +491,7 @@
     <col min="3" max="3" width="25.7109375" customWidth="1"/>
     <col min="4" max="4" width="26.140625" customWidth="1"/>
     <col min="5" max="5" width="21.42578125" customWidth="1"/>
-    <col min="6" max="6" width="39.7109375" customWidth="1"/>
+    <col min="6" max="6" width="25.85546875" customWidth="1"/>
     <col min="7" max="7" width="16.42578125" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
     <col min="9" max="9" width="13.7109375" customWidth="1"/>
@@ -494,122 +500,192 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2"/>
+      <c r="G1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="3" t="s">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="2"/>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="F2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="3"/>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>20</v>
+      <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="C10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F10" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I10" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" t="s">
+        <v>23</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="9">
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="G1:G2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="J1:J2"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="E1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
@@ -628,18 +704,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/SHET/ZPO001/zpovn1.xlsx
+++ b/SHET/ZPO001/zpovn1.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1373AF5E-78C8-4EEB-AA1A-4EA1EBEB0157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C196F795-A549-4B39-859E-48041E34109D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39885" yWindow="2745" windowWidth="35625" windowHeight="14205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -47,24 +47,15 @@
     <t>Iмакс, А</t>
   </si>
   <si>
-    <t>AN</t>
-  </si>
-  <si>
     <t>X:1, X:2</t>
   </si>
   <si>
     <t>ЗПО АТ/ РТ ЗПО ВН: РТ 1</t>
   </si>
   <si>
-    <t>BN</t>
-  </si>
-  <si>
     <t>X:3, X:4</t>
   </si>
   <si>
-    <t>CN</t>
-  </si>
-  <si>
     <t>X:5, X:6</t>
   </si>
   <si>
@@ -96,6 +87,15 @@
   </si>
   <si>
     <t>ТС</t>
+  </si>
+  <si>
+    <t>Ia ВН</t>
+  </si>
+  <si>
+    <t>Ib ВН</t>
+  </si>
+  <si>
+    <t>Ic ВН</t>
   </si>
 </sst>
 </file>
@@ -501,13 +501,13 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>0</v>
@@ -547,145 +547,145 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F10" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H10" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I10" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J10" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:D2"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="J1:J2"/>
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="G1:G2"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
@@ -704,18 +704,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
